--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 4 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8798D671-E798-4ABF-823C-27E61BC2478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 4 - Copia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8798D671-E798-4ABF-823C-27E61BC2478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 2 3 4 - Copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8798D671-E798-4ABF-823C-27E61BC2478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8798D671-E798-4ABF-823C-27E61BC2478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB4480DF-88A7-4217-9079-EAAA812B55DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -550,7 +550,7 @@
     <t>EMAIL</t>
   </si>
   <si>
-    <t>alexandre_royal@seduc.to.gov.br</t>
+    <t>tolentinoalexandre534@gmail.com</t>
   </si>
 </sst>
 </file>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 2 3 4 - Copia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 - Copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A922E34-2400-4662-B866-7E72EB5AF2F1}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4282688-C39D-4670-B7DB-FA9767DC674A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="236">
   <si>
     <t>CPF</t>
   </si>
@@ -484,17 +484,272 @@
     <t>alline.lira@professor.to.gov.br</t>
   </si>
   <si>
+    <t>andrea.pina@professor.to.gov.br</t>
+  </si>
+  <si>
     <t>ANDRÉA MARTINS DE PINA</t>
   </si>
   <si>
-    <t>andrea.pina@professor.to.gov.br</t>
+    <t>KEILA DUARTE LIMA ROSA</t>
+  </si>
+  <si>
+    <t>ZILMA SALES DE SOUZA</t>
+  </si>
+  <si>
+    <t>LUSIVONE GONCALVES ABREU PINHEIRO</t>
+  </si>
+  <si>
+    <t>ELIANE ALVES DE AZEVEDO SANTANA</t>
+  </si>
+  <si>
+    <t>DEBORA REGINA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>LUCIANA PEREIRA GOMES</t>
+  </si>
+  <si>
+    <t>JULIANA FRASCARI PINTO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>MARIA IRANY BARBOSA PINTO</t>
+  </si>
+  <si>
+    <t>REIJANE ALVES DOS SANTOS MACEDO</t>
+  </si>
+  <si>
+    <t>ROSANGELA MENDES MACIEL SANTOS</t>
+  </si>
+  <si>
+    <t>LUDIMILLA RAMOS SILVA BEZERRA</t>
+  </si>
+  <si>
+    <t>SUENNY FERREIRA CRUZ</t>
+  </si>
+  <si>
+    <t>POLLYANA DE GODOY BORGES</t>
+  </si>
+  <si>
+    <t>SYNARA NUNES RIBEIRO</t>
+  </si>
+  <si>
+    <t>ELIUDE FERNANDES DA SILVA MOURA</t>
+  </si>
+  <si>
+    <t>MARIA JOANA MONTEIRO PORTILHO BARROS</t>
+  </si>
+  <si>
+    <t>POLIANA FERREIRA DE MOURA COÊLHO</t>
+  </si>
+  <si>
+    <t>LINA MARIA DA SILVA CONCESSO</t>
+  </si>
+  <si>
+    <t>AYRANA GOMES FERREIRA</t>
+  </si>
+  <si>
+    <t>ROSEANE SOUZA PEREIRA</t>
+  </si>
+  <si>
+    <t>LIDIANE RODRIGUES PEREIRA</t>
+  </si>
+  <si>
+    <t>ALINE REIS DOS SANTOS MARTINS</t>
+  </si>
+  <si>
+    <t>MARLI FERREIRA VIEIRA FONSECA</t>
+  </si>
+  <si>
+    <t>VIVIANO IESORU JAVAÉ KARAJÁ</t>
+  </si>
+  <si>
+    <t>CLAUDILENE SEIJA TORRES JAVAÉ</t>
+  </si>
+  <si>
+    <t>ORLENE DE SOUSA R. JÁCOME</t>
+  </si>
+  <si>
+    <t>VALDIRENE ALVES LIMA</t>
+  </si>
+  <si>
+    <t>MARIA DE FÁTIMA MARQUES DE OLIVEIRA SANTANA</t>
+  </si>
+  <si>
+    <t>626.250.041-34</t>
+  </si>
+  <si>
+    <t>623.532.171-68</t>
+  </si>
+  <si>
+    <t>575.111.281-49</t>
+  </si>
+  <si>
+    <t>758.444.861-53</t>
+  </si>
+  <si>
+    <t>371.383.751-15</t>
+  </si>
+  <si>
+    <t>008.869.971-43</t>
+  </si>
+  <si>
+    <t>038.389.916-80</t>
+  </si>
+  <si>
+    <t>003.073.171-29</t>
+  </si>
+  <si>
+    <t>012.087.871-28</t>
+  </si>
+  <si>
+    <t>827.967.001-78</t>
+  </si>
+  <si>
+    <t>000.010.751-44</t>
+  </si>
+  <si>
+    <t>003.885.911-45</t>
+  </si>
+  <si>
+    <t>014.827.731-47</t>
+  </si>
+  <si>
+    <t>882.447.251-68</t>
+  </si>
+  <si>
+    <t>985.670.631-91</t>
+  </si>
+  <si>
+    <t>800.627.251-49</t>
+  </si>
+  <si>
+    <t>019.762.211-96</t>
+  </si>
+  <si>
+    <t>340.951.601-87</t>
+  </si>
+  <si>
+    <t>076.079.991-16</t>
+  </si>
+  <si>
+    <t>034.963.001-16</t>
+  </si>
+  <si>
+    <t>010.515.591-89</t>
+  </si>
+  <si>
+    <t>066.914.441-08</t>
+  </si>
+  <si>
+    <t>435.003.151-00</t>
+  </si>
+  <si>
+    <t>016.528.091-39</t>
+  </si>
+  <si>
+    <t>071.338.531-67</t>
+  </si>
+  <si>
+    <t>451.680.081-00</t>
+  </si>
+  <si>
+    <t>006.309.481-94</t>
+  </si>
+  <si>
+    <t>315.567.871-20</t>
+  </si>
+  <si>
+    <t>964.858.761-20</t>
+  </si>
+  <si>
+    <t>lusivoneabreu01@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>elianeasantana@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>deboraazevedo@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>lucianapereiragomes@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>julianafrascarioliveira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>mariairanypinto17@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>reijanealvesmacedo@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>rosangelammaciel@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>Não Possui (E preciso solicitar)</t>
+  </si>
+  <si>
+    <t>suennycruz@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>pollyana.borges@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>synararibeiro@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>eliudesilvamoura@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>mariajoanaportilhobarros@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>poliana.coelho@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>lina.concesso@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ayrana.ferreira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>roseanesouza@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>lidiane.pereira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>marlifonseca@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>vivianokaraja202323@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>claudilene.javae@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>orlene.jacome@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>valdirene.lima@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>maria.fatimasantana@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrea.pina@professor.to.gov.br </t>
+  </si>
+  <si>
+    <t>zilmaribeiro@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keilarosa@seduc.to.gov.br </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -517,6 +772,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -526,7 +787,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -534,12 +795,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -547,6 +823,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -563,6 +842,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -862,13 +1145,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1827,11 +2110,374 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="E71" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1895,8 +2541,11 @@
     <hyperlink ref="E69" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
     <hyperlink ref="E70" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
     <hyperlink ref="E7" r:id="rId58" xr:uid="{837AFF8C-CBEC-495D-8C54-2EF7EE097514}"/>
+    <hyperlink ref="E71" r:id="rId59" xr:uid="{8578D14F-F5C7-4B4F-9324-52C4E9DDA4D9}"/>
+    <hyperlink ref="E72" r:id="rId60" xr:uid="{03D3228E-2A04-4F16-B558-0099E265701C}"/>
+    <hyperlink ref="E90" r:id="rId61" xr:uid="{8426E286-B438-4344-82EE-CEE4BC8593E7}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId62"/>
 </worksheet>
 </file>